--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260930.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260930.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16659,7 +16659,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17530,7 +17530,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17865,7 +17865,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18736,7 +18736,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19674,7 +19674,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20746,7 +20746,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20880,7 +20880,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21148,7 +21148,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21751,7 +21751,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21885,7 +21885,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22421,7 +22421,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22689,7 +22689,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22823,7 +22823,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S339" t="inlineStr"/>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S340" t="inlineStr"/>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S341" t="inlineStr"/>
@@ -23423,7 +23423,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="S342" t="inlineStr"/>
